--- a/rating for Chatbot answers.xlsx
+++ b/rating for Chatbot answers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junjiezhang/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20627D22-CE8B-684A-AD7E-32C6FE796431}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B353D5C-4F62-BF43-9F89-855FA8D25817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-8780" windowWidth="38400" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="-8780" windowWidth="38400" windowHeight="19720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Shuming" sheetId="1" r:id="rId1"/>
@@ -1104,7 +1104,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C2">
         <f>AVERAGE(Shuming!J2,JJ!B2)</f>
@@ -1123,7 +1123,7 @@
         <v>13</v>
       </c>
       <c r="G2">
-        <v>0.86299999999999999</v>
+        <v>0.86399999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.15">
@@ -1131,7 +1131,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C3">
         <f>AVERAGE(Shuming!N2,JJ!F2)</f>
@@ -1150,7 +1150,7 @@
         <v>15</v>
       </c>
       <c r="G3">
-        <v>0.86399999999999999</v>
+        <v>0.86299999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
@@ -1158,7 +1158,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C4">
         <f>AVERAGE(Shuming!J3,JJ!B3)</f>
@@ -1177,7 +1177,7 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>0.63400000000000001</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.15">
@@ -1185,7 +1185,7 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <f>AVERAGE(Shuming!N3,JJ!F3)</f>
@@ -1204,7 +1204,7 @@
         <v>15</v>
       </c>
       <c r="G5">
-        <v>0.62</v>
+        <v>0.63400000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.15">
@@ -1212,7 +1212,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C6">
         <f>AVERAGE(Shuming!J4,JJ!B4)</f>
@@ -1231,7 +1231,7 @@
         <v>14</v>
       </c>
       <c r="G6">
-        <v>0.95799999999999996</v>
+        <v>0.96199999999999997</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.15">
@@ -1239,7 +1239,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C7">
         <f>AVERAGE(Shuming!N4,JJ!F4)</f>
@@ -1258,7 +1258,7 @@
         <v>15</v>
       </c>
       <c r="G7">
-        <v>0.96199999999999997</v>
+        <v>0.95799999999999996</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.15">
@@ -1266,7 +1266,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C8">
         <f>AVERAGE(Shuming!J5,JJ!B5)</f>
@@ -1285,7 +1285,7 @@
         <v>13</v>
       </c>
       <c r="G8">
-        <v>0.94199999999999995</v>
+        <v>0.94299999999999995</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.15">
@@ -1293,7 +1293,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C9">
         <f>AVERAGE(Shuming!N5,JJ!F5)</f>
@@ -1312,7 +1312,7 @@
         <v>15</v>
       </c>
       <c r="G9">
-        <v>0.94299999999999995</v>
+        <v>0.94199999999999995</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.15">
@@ -1320,7 +1320,7 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C10">
         <f>AVERAGE(Shuming!J6,JJ!B6)</f>
@@ -1339,7 +1339,7 @@
         <v>15</v>
       </c>
       <c r="G10">
-        <v>0.88100000000000001</v>
+        <v>0.96199999999999997</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.15">
@@ -1347,7 +1347,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C11">
         <f>AVERAGE(Shuming!N6,JJ!F6)</f>
@@ -1366,7 +1366,7 @@
         <v>15</v>
       </c>
       <c r="G11">
-        <v>0.96199999999999997</v>
+        <v>0.88100000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.15">
@@ -1374,7 +1374,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C12">
         <f>AVERAGE(Shuming!J7,JJ!B7)</f>
@@ -1393,7 +1393,7 @@
         <v>13</v>
       </c>
       <c r="G12">
-        <v>0.57399999999999995</v>
+        <v>0.66200000000000003</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.15">
@@ -1401,7 +1401,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C13">
         <f>AVERAGE(Shuming!N7,JJ!F7)</f>
@@ -1420,7 +1420,7 @@
         <v>15</v>
       </c>
       <c r="G13">
-        <v>0.66200000000000003</v>
+        <v>0.57399999999999995</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.15">
@@ -1428,7 +1428,7 @@
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <f>AVERAGE(Shuming!J8,JJ!B8)</f>
@@ -1447,7 +1447,7 @@
         <v>2</v>
       </c>
       <c r="G14">
-        <v>0.93400000000000005</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.15">
@@ -1455,7 +1455,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C15">
         <f>AVERAGE(Shuming!N8,JJ!F8)</f>
@@ -1474,7 +1474,7 @@
         <v>15</v>
       </c>
       <c r="G15">
-        <v>0.68</v>
+        <v>0.93400000000000005</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.15">
@@ -1482,7 +1482,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C16">
         <f>AVERAGE(Shuming!J9,JJ!B9)</f>
@@ -1501,7 +1501,7 @@
         <v>2</v>
       </c>
       <c r="G16">
-        <v>0.88700000000000001</v>
+        <v>0.63900000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.15">
@@ -1509,7 +1509,7 @@
         <v>8</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C17">
         <f>AVERAGE(Shuming!N9,JJ!F9)</f>
@@ -1528,7 +1528,7 @@
         <v>15</v>
       </c>
       <c r="G17">
-        <v>0.63900000000000001</v>
+        <v>0.88700000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.15">
@@ -1536,7 +1536,7 @@
         <v>9</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C18">
         <f>AVERAGE(Shuming!J10,JJ!B10)</f>
@@ -1555,7 +1555,7 @@
         <v>2</v>
       </c>
       <c r="G18">
-        <v>0.93200000000000005</v>
+        <v>0.84499999999999997</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.15">
@@ -1563,7 +1563,7 @@
         <v>9</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C19">
         <f>AVERAGE(Shuming!N10,JJ!F10)</f>
@@ -1582,7 +1582,7 @@
         <v>15</v>
       </c>
       <c r="G19">
-        <v>0.84499999999999997</v>
+        <v>0.93200000000000005</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.15">
@@ -1590,7 +1590,7 @@
         <v>10</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C20">
         <f>AVERAGE(Shuming!J11,JJ!B11)</f>
@@ -1609,7 +1609,7 @@
         <v>11</v>
       </c>
       <c r="G20">
-        <v>0.80200000000000005</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.15">
@@ -1617,7 +1617,7 @@
         <v>10</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C21">
         <f>AVERAGE(Shuming!N11,JJ!F11)</f>
@@ -1636,7 +1636,7 @@
         <v>13</v>
       </c>
       <c r="G21">
-        <v>0.65</v>
+        <v>0.80200000000000005</v>
       </c>
     </row>
   </sheetData>

--- a/rating for Chatbot answers.xlsx
+++ b/rating for Chatbot answers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junjiezhang/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B353D5C-4F62-BF43-9F89-855FA8D25817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84BF864-3D82-9B4E-B857-0AA2F835D4C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="-8780" windowWidth="38400" windowHeight="19720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="sum" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">sum!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">sum!$A$1:$H$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="30">
   <si>
     <t>Answer to Question</t>
   </si>
@@ -67,38 +67,83 @@
     <t>Version 2 Total</t>
   </si>
   <si>
-    <t>question</t>
-  </si>
-  <si>
-    <t>answer by RAG</t>
-  </si>
-  <si>
     <t>Yes</t>
   </si>
   <si>
     <t>Relevancy</t>
   </si>
   <si>
-    <t xml:space="preserve">Accuracy  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluency </t>
-  </si>
-  <si>
     <t>Overall</t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
-    <t>Cos similarity</t>
+    <t>Retrieval_Time(s)</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What are adaptive designs for medical device clinical study
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How treatment policy strategy is used for Addressing Intercurrent Events when Defining the Clinical Question of Interest
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is a predictive distribution?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What is exchangeability?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How to determine the sample size when using Bayesian method for a clinical trial:
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What are Noninferiority Trials
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What are the methods for the calculation of the between subject coefficient of variation as stated in SOP- BMD-4002?
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What level of precision of PK Parameters from WinNonlin is needed for PK reporting?
+</t>
+  </si>
+  <si>
+    <t>List Non-numeric PK Concentration values and their meaning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What are the Trial Master File content and responsible role related to required documentation for randomization process?
+</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>Fluency</t>
+  </si>
+  <si>
+    <t>Cos_similarity</t>
+  </si>
+  <si>
+    <t>RAG_used</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -115,6 +160,13 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF262730"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -140,10 +192,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -710,6 +766,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -1065,586 +1122,715 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0A394B9-5402-C548-AF95-9B906B1554EA}">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="2" max="2" width="67.6640625" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.15">
+    </row>
+    <row r="2" spans="1:9" ht="28" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2">
         <f>AVERAGE(Shuming!J2,JJ!B2)</f>
         <v>4</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <f>AVERAGE(Shuming!K2,JJ!C2)</f>
         <v>5</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <f>AVERAGE(Shuming!L2,JJ!D2)</f>
         <v>4</v>
       </c>
-      <c r="F2">
+      <c r="G2">
         <f>AVERAGE(Shuming!M2,JJ!E2)</f>
         <v>13</v>
       </c>
-      <c r="G2">
-        <v>0.86399999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H2">
+        <v>0.25</v>
+      </c>
+      <c r="I2">
+        <v>0.23699999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3">
+      <c r="B3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3">
         <f>AVERAGE(Shuming!N2,JJ!F2)</f>
         <v>5</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <f>AVERAGE(Shuming!O2,JJ!G2)</f>
         <v>5</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <f>AVERAGE(Shuming!P2,JJ!H2)</f>
         <v>5</v>
       </c>
-      <c r="F3">
+      <c r="G3">
         <f>AVERAGE(Shuming!Q2,JJ!I2)</f>
         <v>15</v>
       </c>
-      <c r="G3">
-        <v>0.86299999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H3">
+        <v>0.85899999999999999</v>
+      </c>
+      <c r="I3">
+        <v>2.27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="42" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4">
+      <c r="B4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4">
         <f>AVERAGE(Shuming!J3,JJ!B3)</f>
         <v>3</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <f>AVERAGE(Shuming!K3,JJ!C3)</f>
         <v>5</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <f>AVERAGE(Shuming!L3,JJ!D3)</f>
         <v>3</v>
       </c>
-      <c r="F4">
+      <c r="G4">
         <f>AVERAGE(Shuming!M3,JJ!E3)</f>
         <v>11</v>
       </c>
-      <c r="G4">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H4">
+        <v>0.41099999999999998</v>
+      </c>
+      <c r="I4">
+        <v>0.14799999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="42" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>2</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5">
+      <c r="B5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5">
         <f>AVERAGE(Shuming!N3,JJ!F3)</f>
         <v>5</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <f>AVERAGE(Shuming!O3,JJ!G3)</f>
         <v>5</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <f>AVERAGE(Shuming!P3,JJ!H3)</f>
         <v>5</v>
       </c>
-      <c r="F5">
+      <c r="G5">
         <f>AVERAGE(Shuming!Q3,JJ!I3)</f>
         <v>15</v>
       </c>
-      <c r="G5">
-        <v>0.63400000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H5">
+        <v>0.57799999999999996</v>
+      </c>
+      <c r="I5">
+        <v>2.6110000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="28" x14ac:dyDescent="0.15">
       <c r="A6">
         <v>3</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6">
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6">
         <f>AVERAGE(Shuming!J4,JJ!B4)</f>
         <v>5</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <f>AVERAGE(Shuming!K4,JJ!C4)</f>
         <v>4</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <f>AVERAGE(Shuming!L4,JJ!D4)</f>
         <v>5</v>
       </c>
-      <c r="F6">
+      <c r="G6">
         <f>AVERAGE(Shuming!M4,JJ!E4)</f>
         <v>14</v>
       </c>
-      <c r="G6">
-        <v>0.96199999999999997</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H6">
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="I6">
+        <v>0.16200000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="28" x14ac:dyDescent="0.15">
       <c r="A7">
         <v>3</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7">
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7">
         <f>AVERAGE(Shuming!N4,JJ!F4)</f>
         <v>5</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <f>AVERAGE(Shuming!O4,JJ!G4)</f>
         <v>5</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <f>AVERAGE(Shuming!P4,JJ!H4)</f>
         <v>5</v>
       </c>
-      <c r="F7">
+      <c r="G7">
         <f>AVERAGE(Shuming!Q4,JJ!I4)</f>
         <v>15</v>
       </c>
-      <c r="G7">
-        <v>0.95799999999999996</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H7">
+        <v>0.95599999999999996</v>
+      </c>
+      <c r="I7">
+        <v>2.5219999999999998</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="28" x14ac:dyDescent="0.15">
       <c r="A8">
         <v>4</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8">
+      <c r="B8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8">
         <f>AVERAGE(Shuming!J5,JJ!B5)</f>
         <v>5</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <f>AVERAGE(Shuming!K5,JJ!C5)</f>
         <v>3</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <f>AVERAGE(Shuming!L5,JJ!D5)</f>
         <v>5</v>
       </c>
-      <c r="F8">
+      <c r="G8">
         <f>AVERAGE(Shuming!M5,JJ!E5)</f>
         <v>13</v>
       </c>
-      <c r="G8">
-        <v>0.94299999999999995</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H8">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="I8">
+        <v>0.13700000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="28" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>4</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9">
+      <c r="B9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9">
         <f>AVERAGE(Shuming!N5,JJ!F5)</f>
         <v>5</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <f>AVERAGE(Shuming!O5,JJ!G5)</f>
         <v>5</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <f>AVERAGE(Shuming!P5,JJ!H5)</f>
         <v>5</v>
       </c>
-      <c r="F9">
+      <c r="G9">
         <f>AVERAGE(Shuming!Q5,JJ!I5)</f>
         <v>15</v>
       </c>
-      <c r="G9">
-        <v>0.94199999999999995</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H9">
+        <v>0.93600000000000005</v>
+      </c>
+      <c r="I9">
+        <v>3.2330000000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="28" x14ac:dyDescent="0.15">
       <c r="A10">
         <v>5</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10">
+      <c r="B10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10">
         <f>AVERAGE(Shuming!J6,JJ!B6)</f>
         <v>5</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <f>AVERAGE(Shuming!K6,JJ!C6)</f>
         <v>5</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <f>AVERAGE(Shuming!L6,JJ!D6)</f>
         <v>5</v>
       </c>
-      <c r="F10">
+      <c r="G10">
         <f>AVERAGE(Shuming!M6,JJ!E6)</f>
         <v>15</v>
       </c>
-      <c r="G10">
-        <v>0.96199999999999997</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H10">
+        <v>0.30099999999999999</v>
+      </c>
+      <c r="I10">
+        <v>0.19800000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="28" x14ac:dyDescent="0.15">
       <c r="A11">
         <v>5</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11">
+      <c r="B11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11">
         <f>AVERAGE(Shuming!N6,JJ!F6)</f>
         <v>5</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <f>AVERAGE(Shuming!O6,JJ!G6)</f>
         <v>5</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <f>AVERAGE(Shuming!P6,JJ!H6)</f>
         <v>5</v>
       </c>
-      <c r="F11">
+      <c r="G11">
         <f>AVERAGE(Shuming!Q6,JJ!I6)</f>
         <v>15</v>
       </c>
-      <c r="G11">
-        <v>0.88100000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H11">
+        <v>0.85299999999999998</v>
+      </c>
+      <c r="I11">
+        <v>2.573</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="28" x14ac:dyDescent="0.15">
       <c r="A12">
         <v>6</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12">
+      <c r="B12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12">
         <f>AVERAGE(Shuming!J7,JJ!B7)</f>
         <v>4</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <f>AVERAGE(Shuming!K7,JJ!C7)</f>
         <v>4</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <f>AVERAGE(Shuming!L7,JJ!D7)</f>
         <v>5</v>
       </c>
-      <c r="F12">
+      <c r="G12">
         <f>AVERAGE(Shuming!M7,JJ!E7)</f>
         <v>13</v>
       </c>
-      <c r="G12">
-        <v>0.66200000000000003</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H12">
+        <v>0.317</v>
+      </c>
+      <c r="I12">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="28" x14ac:dyDescent="0.15">
       <c r="A13">
         <v>6</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13">
+      <c r="B13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13">
         <f>AVERAGE(Shuming!N7,JJ!F7)</f>
         <v>5</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <f>AVERAGE(Shuming!O7,JJ!G7)</f>
         <v>5</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <f>AVERAGE(Shuming!P7,JJ!H7)</f>
         <v>5</v>
       </c>
-      <c r="F13">
+      <c r="G13">
         <f>AVERAGE(Shuming!Q7,JJ!I7)</f>
         <v>15</v>
       </c>
-      <c r="G13">
-        <v>0.57399999999999995</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H13">
+        <v>0.68300000000000005</v>
+      </c>
+      <c r="I13">
+        <v>3.1659999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="42" x14ac:dyDescent="0.15">
       <c r="A14">
         <v>7</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14">
+      <c r="B14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14">
         <f>AVERAGE(Shuming!J8,JJ!B8)</f>
         <v>0</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <f>AVERAGE(Shuming!K8,JJ!C8)</f>
         <v>1</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <f>AVERAGE(Shuming!L8,JJ!D8)</f>
         <v>1</v>
       </c>
-      <c r="F14">
+      <c r="G14">
         <f>AVERAGE(Shuming!M8,JJ!E8)</f>
         <v>2</v>
       </c>
-      <c r="G14">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H14">
+        <v>0.32</v>
+      </c>
+      <c r="I14">
+        <v>0.158</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="42" x14ac:dyDescent="0.15">
       <c r="A15">
         <v>7</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15">
+      <c r="B15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15">
         <f>AVERAGE(Shuming!N8,JJ!F8)</f>
         <v>5</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <f>AVERAGE(Shuming!O8,JJ!G8)</f>
         <v>5</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <f>AVERAGE(Shuming!P8,JJ!H8)</f>
         <v>5</v>
       </c>
-      <c r="F15">
+      <c r="G15">
         <f>AVERAGE(Shuming!Q8,JJ!I8)</f>
         <v>15</v>
       </c>
-      <c r="G15">
-        <v>0.93400000000000005</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H15">
+        <v>0.92600000000000005</v>
+      </c>
+      <c r="I15">
+        <v>2.6760000000000002</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="28" x14ac:dyDescent="0.15">
       <c r="A16">
         <v>8</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16">
+      <c r="B16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16">
         <f>AVERAGE(Shuming!J9,JJ!B9)</f>
         <v>0</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <f>AVERAGE(Shuming!K9,JJ!C9)</f>
         <v>1</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <f>AVERAGE(Shuming!L9,JJ!D9)</f>
         <v>1</v>
       </c>
-      <c r="F16">
+      <c r="G16">
         <f>AVERAGE(Shuming!M9,JJ!E9)</f>
         <v>2</v>
       </c>
-      <c r="G16">
-        <v>0.63900000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H16">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="I16">
+        <v>0.152</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="28" x14ac:dyDescent="0.15">
       <c r="A17">
         <v>8</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17">
+      <c r="B17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17">
         <f>AVERAGE(Shuming!N9,JJ!F9)</f>
         <v>5</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <f>AVERAGE(Shuming!O9,JJ!G9)</f>
         <v>5</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <f>AVERAGE(Shuming!P9,JJ!H9)</f>
         <v>5</v>
       </c>
-      <c r="F17">
+      <c r="G17">
         <f>AVERAGE(Shuming!Q9,JJ!I9)</f>
         <v>15</v>
       </c>
-      <c r="G17">
-        <v>0.88700000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H17">
+        <v>0.87</v>
+      </c>
+      <c r="I17">
+        <v>1.9179999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18">
         <v>9</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18">
+      <c r="B18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18">
         <f>AVERAGE(Shuming!J10,JJ!B10)</f>
         <v>0</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <f>AVERAGE(Shuming!K10,JJ!C10)</f>
         <v>1</v>
       </c>
-      <c r="E18">
+      <c r="F18">
         <f>AVERAGE(Shuming!L10,JJ!D10)</f>
         <v>1</v>
       </c>
-      <c r="F18">
+      <c r="G18">
         <f>AVERAGE(Shuming!M10,JJ!E10)</f>
         <v>2</v>
       </c>
-      <c r="G18">
-        <v>0.84499999999999997</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H18">
+        <v>0.124</v>
+      </c>
+      <c r="I18">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A19">
         <v>9</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19">
+      <c r="B19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19">
         <f>AVERAGE(Shuming!N10,JJ!F10)</f>
         <v>5</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <f>AVERAGE(Shuming!O10,JJ!G10)</f>
         <v>5</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <f>AVERAGE(Shuming!P10,JJ!H10)</f>
         <v>5</v>
       </c>
-      <c r="F19">
+      <c r="G19">
         <f>AVERAGE(Shuming!Q10,JJ!I10)</f>
         <v>15</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>0.93200000000000005</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="I19">
+        <v>1.1879999999999999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="42" x14ac:dyDescent="0.15">
       <c r="A20">
         <v>10</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20">
+      <c r="B20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20">
         <f>AVERAGE(Shuming!J11,JJ!B11)</f>
         <v>3</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <f>AVERAGE(Shuming!K11,JJ!C11)</f>
         <v>4</v>
       </c>
-      <c r="E20">
+      <c r="F20">
         <f>AVERAGE(Shuming!L11,JJ!D11)</f>
         <v>4</v>
       </c>
-      <c r="F20">
+      <c r="G20">
         <f>AVERAGE(Shuming!M11,JJ!E11)</f>
         <v>11</v>
       </c>
-      <c r="G20">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="H20">
+        <v>0.26200000000000001</v>
+      </c>
+      <c r="I20">
+        <v>0.193</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="42" x14ac:dyDescent="0.15">
       <c r="A21">
         <v>10</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21">
+      <c r="B21" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21">
         <f>AVERAGE(Shuming!N11,JJ!F11)</f>
         <v>4</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <f>AVERAGE(Shuming!O11,JJ!G11)</f>
         <v>4</v>
       </c>
-      <c r="E21">
+      <c r="F21">
         <f>AVERAGE(Shuming!P11,JJ!H11)</f>
         <v>5</v>
       </c>
-      <c r="F21">
+      <c r="G21">
         <f>AVERAGE(Shuming!Q11,JJ!I11)</f>
         <v>13</v>
       </c>
-      <c r="G21">
-        <v>0.80200000000000005</v>
+      <c r="H21">
+        <v>0.82</v>
+      </c>
+      <c r="I21">
+        <v>4.03</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G1" xr:uid="{C0A394B9-5402-C548-AF95-9B906B1554EA}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G21">
+  <autoFilter ref="A1:H21" xr:uid="{C0A394B9-5402-C548-AF95-9B906B1554EA}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H21">
       <sortCondition ref="A1:A21"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>